--- a/backend/data/processed/projects_overlaps.xlsx
+++ b/backend/data/processed/projects_overlaps.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD72"/>
+  <dimension ref="A1:AE72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,135 +439,140 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>project_type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>name_a</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name_b</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>lat_a</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>lon_a</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>lat_b</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>lon_b</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>lat_center</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>lon_center</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>in_service_date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>location_confidence</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>source_kind</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>overlap_count</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>overlap_1</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>overlap_2</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>overlap_3</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>overlap_4</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>overlap_5</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>overlap_6</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>overlap_7</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>overlap_8</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>overlap_9</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>overlap_10</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>overlap_11</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>overlap_12</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>overlap_13</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>overlap_14</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>overlap_15</t>
         </is>
@@ -591,103 +596,108 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>substation</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Okatie</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
         <v>32.277554</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>-80.968648</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
         <v>32.277554</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>-80.968648</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="M2" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>12</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>OVL_8</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>OVL_24</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>OVL_36</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>OVL_37</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>OVL_39</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>OVL_49</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>OVL_70</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>OVL_71</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>OVL_72</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>OVL_89</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>OVL_91</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>OVL_105</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -707,45 +717,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>new_line</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Jack Primus</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Clements Ferry</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>32.9193841</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>-79.9044954</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
         <v>32.9193841</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>-79.9044954</v>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="M3" s="1" t="n">
         <v>46752</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
@@ -760,6 +774,7 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -779,45 +794,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>new_line</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Cainhoy</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Clements Ferry</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>32.941402</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>-79.8422757</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>32.941402</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>-79.8422757</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="M4" s="1" t="n">
         <v>46752</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
@@ -832,6 +851,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -851,41 +871,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Columbia Canal</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
         <v>33.9971705</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>-81.04928719999999</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
         <v>33.9971705</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>-81.04928719999999</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="M5" s="1" t="n">
         <v>46173</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
@@ -900,6 +924,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -919,41 +944,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>new_line</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Harleyville</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
         <v>33.2099069</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-80.4511658</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
         <v>33.2099069</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>-80.4511658</v>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="M6" s="1" t="n">
         <v>46477</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
@@ -968,6 +997,7 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -987,45 +1017,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Canadys</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Ritter</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>33.0640963</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>-80.6205999</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
         <v>33.0640963</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>-80.6205999</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
@@ -1040,6 +1074,7 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1059,107 +1094,112 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>new_line</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Okatie</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Riverport</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>32.277554</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>-80.968648</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
         <v>32.277554</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>-80.968648</v>
       </c>
-      <c r="L8" s="1" t="n">
+      <c r="M8" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>12</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>OVL_4</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>OVL_22</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>OVL_23</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>OVL_25</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>OVL_27</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>OVL_61</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>OVL_62</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>OVL_64</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>OVL_73</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>OVL_90</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>OVL_92</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>OVL_104</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1179,119 +1219,124 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>new_line</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Jasper</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Okatie</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>32.3591202</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>-81.1245996</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>32.277554</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>-80.968648</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>32.3183371</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>-81.04662379999999</v>
       </c>
-      <c r="L9" s="1" t="n">
+      <c r="M9" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>15</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>OVL_1</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>OVL_7</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>OVL_18</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>OVL_32</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>OVL_33</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>OVL_47</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>OVL_50</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>OVL_54</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>OVL_57</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>OVL_66</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>OVL_75</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>OVL_78</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>OVL_86</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>OVL_93</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>OVL_103</t>
         </is>
@@ -1315,41 +1360,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>new_line</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Wagener</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
         <v>33.6501119</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-81.3605659</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
         <v>33.6501119</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-81.3605659</v>
       </c>
-      <c r="L10" s="1" t="n">
+      <c r="M10" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -1364,6 +1413,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1383,45 +1433,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Church Creek</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Ritter</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>32.8303196</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>-80.0702792</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
         <v>32.8303196</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>-80.0702792</v>
       </c>
-      <c r="L11" s="1" t="n">
+      <c r="M11" s="1" t="n">
         <v>45444</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1436,6 +1490,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1455,41 +1510,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="n">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
         <v>33.87218</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-81.69772279999999</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
         <v>33.87218</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>-81.69772279999999</v>
       </c>
-      <c r="L12" s="1" t="n">
+      <c r="M12" s="1" t="n">
         <v>47483</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1504,6 +1563,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1523,41 +1583,45 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>substation</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Williams St</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="n">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
         <v>35.0491473</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>-78.8864018</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
         <v>35.0491473</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>-78.8864018</v>
       </c>
-      <c r="L13" s="1" t="n">
+      <c r="M13" s="1" t="n">
         <v>47118</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1572,6 +1636,7 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1591,49 +1656,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Fairfax</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Yemassee</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>32.9543755</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>-81.2318604</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>32.6974259</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>-80.86379290000001</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>32.8259007</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>-81.04782665</v>
       </c>
-      <c r="L14" s="1" t="n">
+      <c r="M14" s="1" t="n">
         <v>46637</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -1648,6 +1717,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1667,49 +1737,53 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>new_line</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Cainhoy</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Hamlin</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>32.941402</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>-79.8422757</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>32.859937</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>-79.7884409</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>32.9006695</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-79.8153583</v>
       </c>
-      <c r="L15" s="1" t="n">
+      <c r="M15" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -1724,6 +1798,7 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1743,45 +1818,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>new_line</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Yemassee</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Ritter</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>32.6974259</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>-80.86379290000001</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
         <v>32.6974259</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>-80.86379290000001</v>
       </c>
-      <c r="L16" s="1" t="n">
+      <c r="M16" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -1796,6 +1875,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1815,45 +1895,49 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>Williams</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Summerville</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>33.0176985</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>-79.9321678</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
         <v>33.0176985</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>-79.9321678</v>
       </c>
-      <c r="L17" s="1" t="n">
+      <c r="M17" s="1" t="n">
         <v>46508</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
@@ -1868,6 +1952,7 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1887,41 +1972,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>substation</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Edenwood</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="n">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
         <v>34.1386942</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>-79.826678</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
         <v>34.1386942</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>-79.826678</v>
       </c>
-      <c r="L18" s="1" t="n">
+      <c r="M18" s="1" t="n">
         <v>45651</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -1936,6 +2025,7 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1955,45 +2045,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Queensboro</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Ft Johnson</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>32.7233566</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>-79.9733901</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
         <v>32.7233566</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>-79.9733901</v>
       </c>
-      <c r="L19" s="1" t="n">
+      <c r="M19" s="1" t="n">
         <v>45291</v>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -2008,6 +2102,7 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2027,50 +2122,54 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Burton</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>St Helena</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>32.4364883</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>-80.7210159</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
         <v>32.4364883</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>-80.7210159</v>
       </c>
-      <c r="L20" s="1" t="n">
+      <c r="M20" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>1</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>OVL_63</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2084,6 +2183,7 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2103,50 +2203,54 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Burton</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>St Helena</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>32.4364883</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>-80.7210159</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
         <v>32.4364883</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>-80.7210159</v>
       </c>
-      <c r="L21" s="1" t="n">
+      <c r="M21" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>1</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>OVL_48</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2160,6 +2264,7 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2179,45 +2284,49 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>Denny Terrace</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="n">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
         <v>34.0576091</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>-81.061561</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>32.611892</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>-81.15031329999999</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>33.33475055</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>-81.10593714999999</v>
       </c>
-      <c r="L22" s="1" t="n">
+      <c r="M22" s="1" t="n">
         <v>46387</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
@@ -2232,6 +2341,7 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2251,45 +2361,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Wateree</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Hopkins</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>33.8213074</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>-80.6284218</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
         <v>33.8213074</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>-80.6284218</v>
       </c>
-      <c r="L23" s="1" t="n">
+      <c r="M23" s="1" t="n">
         <v>46752</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -2304,6 +2418,7 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2323,45 +2438,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Wateree</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Killian</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>33.8213074</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>-80.6284218</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
         <v>33.8213074</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-80.6284218</v>
       </c>
-      <c r="L24" s="1" t="n">
+      <c r="M24" s="1" t="n">
         <v>47118</v>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
@@ -2376,6 +2495,7 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2395,103 +2515,108 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Okatie</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Bluffton</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>32.277554</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>-80.968648</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>32.2350272</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>-80.8533836</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>32.2562906</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>-80.9110158</v>
       </c>
-      <c r="L25" s="1" t="n">
+      <c r="M25" s="1" t="n">
         <v>45809</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>10</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>OVL_17</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>OVL_19</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>OVL_35</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>OVL_41</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>OVL_43</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>OVL_74</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>OVL_76</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>OVL_81</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>OVL_97</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>OVL_102</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2511,45 +2636,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Faber Place</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Bayfront</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>32.8500798</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>-80.01462410000001</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
         <v>32.8500798</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>-80.01462410000001</v>
       </c>
-      <c r="L26" s="1" t="n">
+      <c r="M26" s="1" t="n">
         <v>47118</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
@@ -2564,6 +2693,7 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2583,79 +2713,83 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Stevens Creek</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Hooks</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>33.5625993</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>-82.0513618</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>33.65682</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>-82.15947799999999</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>33.60970965</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>-82.10541989999999</v>
       </c>
-      <c r="L27" s="1" t="n">
+      <c r="M27" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>6</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>OVL_13</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>OVL_14</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>OVL_28</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>OVL_45</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>OVL_83</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>OVL_85</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
@@ -2664,6 +2798,7 @@
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2683,49 +2818,53 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Orangeburg</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Cameron Jct</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>33.4595436</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>-80.8889142</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>33.5636663</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>-80.70899590000001</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>33.51160495000001</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>-80.79895505</v>
       </c>
-      <c r="L28" s="1" t="n">
+      <c r="M28" s="1" t="n">
         <v>47118</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
@@ -2740,6 +2879,7 @@
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2759,79 +2899,83 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Stevens Creek</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Hooks</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>33.5625993</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>-82.0513618</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>33.65682</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>-82.15947799999999</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>33.60970965</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>-82.10541989999999</v>
       </c>
-      <c r="L29" s="1" t="n">
+      <c r="M29" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>6</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>OVL_11</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>OVL_12</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>OVL_15</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>OVL_44</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>OVL_82</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>OVL_84</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
@@ -2840,6 +2984,7 @@
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2859,74 +3004,78 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Hooks</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Modoc</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>33.65682</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>-82.15947799999999</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>33.7362884</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>-82.2015043</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>33.6965542</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>-82.18049114999999</v>
       </c>
-      <c r="L30" s="1" t="n">
+      <c r="M30" s="1" t="n">
         <v>46752</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>5</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>OVL_20</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>OVL_21</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>OVL_53</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>OVL_59</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>OVL_87</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -2936,6 +3085,7 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2955,45 +3105,49 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Adams Run</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Red House Road</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>32.7152773</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>-80.3539332</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
         <v>32.7152773</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>-80.3539332</v>
       </c>
-      <c r="L31" s="1" t="n">
+      <c r="M31" s="1" t="n">
         <v>46752</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
@@ -3008,6 +3162,7 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3027,49 +3182,53 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>St George</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Sumter</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>33.199388</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>-80.5920086</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>33.8976611</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>-80.3239761</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>33.54852455</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>-80.45799235</v>
       </c>
-      <c r="L32" s="1" t="n">
+      <c r="M32" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -3084,6 +3243,7 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3103,64 +3263,68 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Modoc</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Mccormick</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>33.7362884</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>-82.2015043</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>33.9065361</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>-82.2928038</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>33.82141224999999</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>-82.24715405000001</v>
       </c>
-      <c r="L33" s="1" t="n">
+      <c r="M33" s="1" t="n">
         <v>47483</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>3</v>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>OVL_55</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>OVL_56</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>OVL_96</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
@@ -3172,6 +3336,7 @@
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3191,45 +3356,49 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Batesburg</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Saluda County</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>33.9134867</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>-81.5644353</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
         <v>33.9134867</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>-81.5644353</v>
       </c>
-      <c r="L34" s="1" t="n">
+      <c r="M34" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
@@ -3244,6 +3413,7 @@
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3263,49 +3433,53 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Cae Industrial Park</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Springdale</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>33.9621858</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>-81.13485319999999</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>33.98202</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>-81.1178417</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>33.9721029</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>-81.12634745</v>
       </c>
-      <c r="L35" s="1" t="n">
+      <c r="M35" s="1" t="n">
         <v>47118</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -3320,6 +3494,7 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3339,74 +3514,78 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Stevens Creek</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Graniteville</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>33.5625993</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>-82.0513618</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>33.5834366</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>-81.804506</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>33.57301795</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>-81.9279339</v>
       </c>
-      <c r="L36" s="1" t="n">
+      <c r="M36" s="1" t="n">
         <v>47483</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>5</v>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>OVL_30</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>OVL_31</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>OVL_51</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>OVL_52</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>OVL_88</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
@@ -3416,6 +3595,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3435,74 +3615,78 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Hooks</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Thurmond</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>33.65682</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>-82.15947799999999</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>33.6601273</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>-82.19593070000001</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>33.65847365</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>-82.17770435</v>
       </c>
-      <c r="L37" s="1" t="n">
+      <c r="M37" s="1" t="n">
         <v>45657</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>5</v>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>OVL_9</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>OVL_10</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>OVL_42</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>OVL_46</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>OVL_77</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
@@ -3512,6 +3696,7 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3531,45 +3716,49 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Elloree</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Santee City</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>33.5323844</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>-80.5797245</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
         <v>33.5323844</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>-80.5797245</v>
       </c>
-      <c r="L38" s="1" t="n">
+      <c r="M38" s="1" t="n">
         <v>46752</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -3584,6 +3773,7 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3603,41 +3793,45 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>North</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
         <v>33.6098839</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>-81.08976389999999</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
         <v>33.6098839</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>-81.08976389999999</v>
       </c>
-      <c r="L39" s="1" t="n">
+      <c r="M39" s="1" t="n">
         <v>47483</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -3652,6 +3846,7 @@
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3671,74 +3866,78 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>Urquhart</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Aiken Psa</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>33.4333777</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>-81.909209</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>33.473195</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>-81.912753</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>33.45328635</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>-81.91098099999999</v>
       </c>
-      <c r="L40" s="1" t="n">
+      <c r="M40" s="1" t="n">
         <v>46752</v>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>OVL_2</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>OVL_26</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>OVL_68</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>OVL_69</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>OVL_94</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
@@ -3748,6 +3947,7 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3767,49 +3967,53 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>Cameron Jct</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Cameron</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>33.5636663</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>-80.70899590000001</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>33.5636663</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>-80.70899590000001</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>33.624865</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>-80.7350057</v>
       </c>
-      <c r="L41" s="1" t="n">
+      <c r="M41" s="1" t="n">
         <v>47118</v>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -3824,6 +4028,7 @@
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3843,49 +4048,53 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>Cameron Jct</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Elloree</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>33.5636663</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>-80.70899590000001</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>33.5323844</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>-80.5797245</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>33.54802535</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>-80.64436019999999</v>
       </c>
-      <c r="L42" s="1" t="n">
+      <c r="M42" s="1" t="n">
         <v>46387</v>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -3900,6 +4109,7 @@
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3919,41 +4129,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>Sumter</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="n">
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="n">
         <v>33.8976611</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>-80.3239761</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
         <v>33.8976611</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>-80.3239761</v>
       </c>
-      <c r="L43" s="1" t="n">
+      <c r="M43" s="1" t="n">
         <v>46173</v>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -3968,6 +4182,7 @@
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3987,49 +4202,53 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>new_line</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Church Creek</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Faber Place</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>32.8303196</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>-80.0702792</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>32.8500798</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>-80.01462410000001</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>32.8401997</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>-80.04245165</v>
       </c>
-      <c r="L44" s="1" t="n">
+      <c r="M44" s="1" t="n">
         <v>46508</v>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
@@ -4044,6 +4263,7 @@
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4063,69 +4283,73 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>Urquhart</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Toolebeck</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>33.4333777</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>-81.909209</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>33.5346321</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>-81.6693272</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>33.4840049</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>-81.7892681</v>
       </c>
-      <c r="L45" s="1" t="n">
+      <c r="M45" s="1" t="n">
         <v>46246</v>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>4</v>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>OVL_3</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>OVL_58</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>OVL_100</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>OVL_101</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
@@ -4136,6 +4360,7 @@
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4155,41 +4380,45 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>new_line</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Church Creek</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="n">
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="n">
         <v>32.8303196</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>-80.0702792</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="n">
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="n">
         <v>32.8303196</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>-80.0702792</v>
       </c>
-      <c r="L46" s="1" t="n">
+      <c r="M46" s="1" t="n">
         <v>47483</v>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -4204,6 +4433,7 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4223,45 +4453,49 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>Saluda Hydro</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Bush River</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>34.0534342</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>-81.2168339</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="n">
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="n">
         <v>34.0534342</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>-81.2168339</v>
       </c>
-      <c r="L47" s="1" t="n">
+      <c r="M47" s="1" t="n">
         <v>46387</v>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
@@ -4276,6 +4510,7 @@
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4295,45 +4530,49 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Church Creek</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Dawson</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>32.8303196</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>-80.0702792</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="n">
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="n">
         <v>32.8303196</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>-80.0702792</v>
       </c>
-      <c r="L48" s="1" t="n">
+      <c r="M48" s="1" t="n">
         <v>47483</v>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
@@ -4348,6 +4587,7 @@
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4367,119 +4607,124 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>substation</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>Okatie</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Mcintosh</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>32.277554</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>-80.968648</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>32.352116</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>-81.175112</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>32.314835</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>-81.07187999999999</v>
       </c>
-      <c r="L49" s="1" t="n">
+      <c r="M49" s="1" t="n">
         <v>47118</v>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>15</v>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>OVL_5</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>OVL_6</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>OVL_16</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>OVL_29</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>OVL_34</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>OVL_38</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>OVL_40</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>OVL_60</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>OVL_65</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>OVL_67</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>OVL_79</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>OVL_80</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>OVL_95</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>OVL_98</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
+      <c r="AE49" t="inlineStr">
         <is>
           <t>OVL_99</t>
         </is>
@@ -4503,61 +4748,65 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>substation</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>Thomson Primary</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="n">
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="n">
         <v>33.453955</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>-82.414219</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="n">
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="n">
         <v>33.453955</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>-82.414219</v>
       </c>
-      <c r="L50" s="1" t="n">
+      <c r="M50" s="1" t="n">
         <v>48731</v>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>4</v>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>OVL_77</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>OVL_82</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>OVL_83</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>OVL_87</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
@@ -4568,6 +4817,7 @@
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr"/>
       <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4587,84 +4837,88 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>Fenwick Street</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Sand Bar Ferry</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>33.46077</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>-81.964742</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>33.442514</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>-81.935045</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>33.451642</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>-81.9498935</v>
       </c>
-      <c r="L51" s="1" t="n">
+      <c r="M51" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>7</v>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>OVL_2</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>OVL_3</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>OVL_15</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>OVL_28</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>OVL_30</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>OVL_46</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>OVL_59</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
@@ -4672,6 +4926,7 @@
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4691,51 +4946,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>substation</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>Little Ogeechee</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="n">
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="n">
         <v>32.0067859</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>-81.2531513</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="n">
         <v>32.0067859</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>-81.2531513</v>
       </c>
-      <c r="L52" s="1" t="n">
+      <c r="M52" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>2</v>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>OVL_47</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>OVL_98</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
@@ -4748,6 +5007,7 @@
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4767,84 +5027,88 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Evans Primary</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Thomson Primary</t>
         </is>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>33.5439942</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>-82.1686481</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>33.453955</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>-82.414219</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>33.4989746</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>-82.29143354999999</v>
       </c>
-      <c r="L53" s="1" t="n">
+      <c r="M53" s="1" t="n">
         <v>49309</v>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>7</v>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>OVL_42</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>OVL_44</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>OVL_45</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>OVL_53</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>OVL_88</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>OVL_94</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>OVL_96</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
@@ -4852,6 +5116,7 @@
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr"/>
       <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4871,61 +5136,65 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>substation</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Meldrim</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="n">
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="n">
         <v>32.1552821</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>-81.368377</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="n">
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="n">
         <v>32.1552821</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>-81.368377</v>
       </c>
-      <c r="L54" s="1" t="n">
+      <c r="M54" s="1" t="n">
         <v>45658</v>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>4</v>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>OVL_49</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>OVL_50</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>OVL_64</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>OVL_80</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
@@ -4936,6 +5205,7 @@
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr"/>
       <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4955,51 +5225,55 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>area_package</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>Little Ogeechee</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="n">
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="n">
         <v>32.0067859</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>-81.2531513</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="n">
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="n">
         <v>32.0067859</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>-81.2531513</v>
       </c>
-      <c r="L55" s="1" t="n">
+      <c r="M55" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>2</v>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>OVL_54</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>OVL_95</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -5012,6 +5286,7 @@
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr"/>
       <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5031,41 +5306,45 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>Warrenton Primary</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="n">
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="n">
         <v>33.3805007</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>-82.687296</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="n">
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="n">
         <v>33.3805007</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>-82.687296</v>
       </c>
-      <c r="L56" s="1" t="n">
+      <c r="M56" s="1" t="n">
         <v>47635</v>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -5080,6 +5359,7 @@
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr"/>
       <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5099,74 +5379,78 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>Goshen (SAV)</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Mcintosh</t>
         </is>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>32.2487012</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>-81.2094724</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>32.3521162</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>-81.1751124</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>32.3004087</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>-81.1922924</v>
       </c>
-      <c r="L57" s="1" t="n">
+      <c r="M57" s="1" t="n">
         <v>46539</v>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>5</v>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>OVL_6</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>OVL_7</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>OVL_22</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>OVL_36</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>OVL_43</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
@@ -5176,6 +5460,7 @@
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5195,74 +5480,78 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>Boulevard</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Deptford</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>32.0412308</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>-81.1444637</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>32.0668279</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>-81.0483845</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>32.05402935</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>-81.09642410000001</v>
       </c>
-      <c r="L58" s="1" t="n">
+      <c r="M58" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>5</v>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>OVL_25</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>OVL_32</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>OVL_35</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>OVL_39</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>OVL_60</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
@@ -5272,6 +5561,7 @@
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr"/>
       <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5291,74 +5581,78 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>Deptford</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Magnolia</t>
         </is>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>32.0668279</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>-81.0483845</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>32.0226869</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>-81.0861807</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>32.04475739999999</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>-81.0672826</v>
       </c>
-      <c r="L59" s="1" t="n">
+      <c r="M59" s="1" t="n">
         <v>45809</v>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>5</v>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>OVL_19</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>OVL_24</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>OVL_27</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>OVL_33</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>OVL_67</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
@@ -5368,6 +5662,7 @@
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr"/>
       <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5387,84 +5682,88 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>substation</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>Mcintosh</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Purrysburg</t>
         </is>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>32.3521162</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>-81.1751124</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>32.335802</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>-81.03144399999999</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>32.3439591</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>-81.10327820000001</v>
       </c>
-      <c r="L60" s="1" t="n">
+      <c r="M60" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>7</v>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>OVL_1</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>OVL_4</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>OVL_5</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>OVL_8</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>OVL_17</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>OVL_48</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>OVL_63</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
@@ -5472,6 +5771,7 @@
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr"/>
       <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5491,70 +5791,74 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>Magnolia</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Truman Parkway</t>
         </is>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>32.0226869</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>-81.0861807</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="n">
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="n">
         <v>32.0226869</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
         <v>-81.0861807</v>
       </c>
-      <c r="L61" s="1" t="n">
+      <c r="M61" s="1" t="n">
         <v>46905</v>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O61" t="n">
+      <c r="P61" t="n">
         <v>5</v>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>OVL_40</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>OVL_62</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>OVL_66</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>OVL_71</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>OVL_74</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
@@ -5564,6 +5868,7 @@
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr"/>
       <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5583,41 +5888,45 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>new_line</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>Wadley</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="n">
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="n">
         <v>32.8846571</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>-82.4158724</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="n">
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
         <v>32.8846571</v>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
         <v>-82.4158724</v>
       </c>
-      <c r="L62" s="1" t="n">
+      <c r="M62" s="1" t="n">
         <v>48000</v>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
@@ -5632,6 +5941,7 @@
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5651,74 +5961,78 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>Coleman</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Dean Forest</t>
         </is>
       </c>
-      <c r="F63" t="n">
+      <c r="G63" t="n">
         <v>32.1077199</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>-81.226912</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>32.0835097</v>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
         <v>-81.18872229999999</v>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
         <v>32.0956148</v>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
         <v>-81.20781715</v>
       </c>
-      <c r="L63" s="1" t="n">
+      <c r="M63" s="1" t="n">
         <v>46905</v>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
         <v>5</v>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>OVL_29</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>OVL_57</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>OVL_61</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>OVL_70</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>OVL_81</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
@@ -5728,6 +6042,7 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr"/>
       <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5747,74 +6062,78 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>Coleman</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Meldrim</t>
         </is>
       </c>
-      <c r="F64" t="n">
+      <c r="G64" t="n">
         <v>32.1077199</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>-81.226912</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>32.1552821</v>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>-81.368377</v>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
         <v>32.131501</v>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
         <v>-81.29764449999999</v>
       </c>
-      <c r="L64" s="1" t="n">
+      <c r="M64" s="1" t="n">
         <v>48366</v>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O64" t="n">
+      <c r="P64" t="n">
         <v>5</v>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>OVL_65</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>OVL_75</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>OVL_89</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>OVL_90</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>OVL_102</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
@@ -5824,6 +6143,7 @@
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr"/>
       <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5843,74 +6163,78 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>Goshen (SAV)</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Kraft</t>
         </is>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>32.2487012</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>-81.2094724</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>32.1481353</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>-81.1459835</v>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
         <v>32.19841825</v>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" t="n">
         <v>-81.17772794999999</v>
       </c>
-      <c r="L65" s="1" t="n">
+      <c r="M65" s="1" t="n">
         <v>46539</v>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O65" t="n">
+      <c r="P65" t="n">
         <v>5</v>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>OVL_16</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>OVL_18</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>OVL_23</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>OVL_37</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>OVL_41</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
@@ -5920,6 +6244,7 @@
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5939,51 +6264,55 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>substation</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>Little Ogeechee</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="n">
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="n">
         <v>32.0067859</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>-81.2531513</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="n">
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="n">
         <v>32.0067859</v>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" t="n">
         <v>-81.2531513</v>
       </c>
-      <c r="L66" s="1" t="n">
+      <c r="M66" s="1" t="n">
         <v>49096</v>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
         <v>2</v>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>OVL_99</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>OVL_103</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
@@ -5996,6 +6325,7 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr"/>
       <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6015,95 +6345,100 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>Evans Primary</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Thurmond Dam</t>
         </is>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>33.5439942</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>-82.1686481</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>33.6601273</v>
       </c>
-      <c r="I67" t="n">
+      <c r="J67" t="n">
         <v>-82.19593070000001</v>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" t="n">
         <v>33.60206075</v>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" t="n">
         <v>-82.1822894</v>
       </c>
-      <c r="L67" s="1" t="n">
+      <c r="M67" s="1" t="n">
         <v>48731</v>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O67" t="n">
+      <c r="P67" t="n">
         <v>8</v>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>OVL_9</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>OVL_12</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>OVL_13</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>OVL_20</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>OVL_51</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>OVL_56</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>OVL_69</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>OVL_100</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr"/>
       <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6123,95 +6458,100 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>Evans Primary</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Thurmond Dam</t>
         </is>
       </c>
-      <c r="F68" t="n">
+      <c r="G68" t="n">
         <v>33.5439942</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>-82.1686481</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>33.6601273</v>
       </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
         <v>-82.19593070000001</v>
       </c>
-      <c r="J68" t="n">
+      <c r="K68" t="n">
         <v>33.60206075</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>-82.1822894</v>
       </c>
-      <c r="L68" s="1" t="n">
+      <c r="M68" s="1" t="n">
         <v>48731</v>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O68" t="n">
+      <c r="P68" t="n">
         <v>8</v>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>OVL_10</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>OVL_11</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>OVL_14</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>OVL_21</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>OVL_52</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>OVL_55</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>OVL_68</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>OVL_101</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr"/>
       <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6231,61 +6571,65 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>substation</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Meldrim</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="n">
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="n">
         <v>32.1552821</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>-81.368377</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="n">
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="n">
         <v>32.1552821</v>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" t="n">
         <v>-81.368377</v>
       </c>
-      <c r="L69" s="1" t="n">
+      <c r="M69" s="1" t="n">
         <v>48731</v>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O69" t="n">
+      <c r="P69" t="n">
         <v>4</v>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>OVL_79</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>OVL_93</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>OVL_104</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>OVL_105</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
@@ -6296,6 +6640,7 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr"/>
       <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6315,74 +6660,78 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>Boulevard</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Magnolia</t>
         </is>
       </c>
-      <c r="F70" t="n">
+      <c r="G70" t="n">
         <v>32.0412308</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>-81.1444637</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>32.0226869</v>
       </c>
-      <c r="I70" t="n">
+      <c r="J70" t="n">
         <v>-81.0861807</v>
       </c>
-      <c r="J70" t="n">
+      <c r="K70" t="n">
         <v>32.03195885</v>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" t="n">
         <v>-81.11532220000001</v>
       </c>
-      <c r="L70" s="1" t="n">
+      <c r="M70" s="1" t="n">
         <v>47270</v>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O70" t="n">
+      <c r="P70" t="n">
         <v>5</v>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>OVL_34</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>OVL_72</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>OVL_73</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>OVL_76</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>OVL_78</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
@@ -6392,6 +6741,7 @@
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr"/>
       <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6411,74 +6761,78 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>line_rebuild</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>Dean Forest</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Little Ogeechee</t>
         </is>
       </c>
-      <c r="F71" t="n">
+      <c r="G71" t="n">
         <v>32.0835097</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>-81.18872229999999</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>32.0067859</v>
       </c>
-      <c r="I71" t="n">
+      <c r="J71" t="n">
         <v>-81.2531513</v>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" t="n">
         <v>32.0451478</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
         <v>-81.2209368</v>
       </c>
-      <c r="L71" s="1" t="n">
+      <c r="M71" s="1" t="n">
         <v>47270</v>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O71" t="n">
+      <c r="P71" t="n">
         <v>5</v>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>OVL_38</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>OVL_86</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>OVL_91</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>OVL_92</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>OVL_97</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
@@ -6488,6 +6842,7 @@
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr"/>
       <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6507,66 +6862,70 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>area_package</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>Goshen</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="n">
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="n">
         <v>33.3197599</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>-81.9953118</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="n">
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="n">
         <v>33.3197599</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
         <v>-81.9953118</v>
       </c>
-      <c r="L72" s="1" t="n">
+      <c r="M72" s="1" t="n">
         <v>47635</v>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>official</t>
         </is>
       </c>
-      <c r="O72" t="n">
+      <c r="P72" t="n">
         <v>5</v>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>OVL_26</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>OVL_31</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>OVL_58</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>OVL_84</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>OVL_85</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
@@ -6576,6 +6935,7 @@
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
